--- a/results/Int Task Remove ACC -0.9/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_5_permute.xlsx
@@ -440,77 +440,77 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6319233075889954</v>
+        <v>0.6254072119811127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6252108210688734</v>
+        <v>0.6002089909026662</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6252108210688734</v>
+        <v>0.6016009730852943</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6199589479641513</v>
+        <v>0.5957398658065824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6204027632694089</v>
+        <v>0.5956645474280534</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6202373444006769</v>
+        <v>0.6039720941887999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6301628284796387</v>
+        <v>0.6089160066336485</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.621779963340363</v>
+        <v>0.6072913821696762</v>
       </c>
     </row>
     <row r="10">
@@ -520,807 +520,807 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6286807458068077</v>
+        <v>0.6083377445031661</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6296894489510332</v>
+        <v>0.6050656184976306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6242116207107239</v>
+        <v>0.6050656184976306</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6225936833925086</v>
+        <v>0.642479847054418</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6291865051990798</v>
+        <v>0.6498015677485295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.652835420192083</v>
+        <v>0.6467782739561718</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6607287158709199</v>
+        <v>0.6425189140638419</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6661178514411855</v>
+        <v>0.6457695708119462</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6698056363487902</v>
+        <v>0.6683320005969158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6674426102112012</v>
+        <v>0.6540436818439066</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6674426102112012</v>
+        <v>0.6432090978969982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6483219487609775</v>
+        <v>0.6451740628845108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6404744072373219</v>
+        <v>0.6294036614586707</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6360872876655245</v>
+        <v>0.6376520797727215</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6297985550133884</v>
+        <v>0.6450047725103405</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.62193341573774</v>
+        <v>0.6378713477625515</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6534274085691197</v>
+        <v>0.6456731351310259</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6515458569260528</v>
+        <v>0.6565925402425392</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6527199789390103</v>
+        <v>0.6611975199840072</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6623508766496132</v>
+        <v>0.6631234179620958</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6616434470195039</v>
+        <v>0.6631234179620958</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6650528354905831</v>
+        <v>0.6631234179620958</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6729676004268511</v>
+        <v>0.6426765899216971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6757367826804332</v>
+        <v>0.6492680039081087</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6766701674461297</v>
+        <v>0.6454605542869531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6821789677299464</v>
+        <v>0.6566583558349922</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6987578098823344</v>
+        <v>0.6495787802083011</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6934844675201811</v>
+        <v>0.6226133928747406</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6713591658947119</v>
+        <v>0.627270813917147</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6674602079631939</v>
+        <v>0.6357761594102923</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6666398007652909</v>
+        <v>0.6662977004665516</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6647515619764669</v>
+        <v>0.6730545333216954</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6647515619764669</v>
+        <v>0.6640099927074916</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6689208213785938</v>
+        <v>0.6549492621614544</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6722615786169012</v>
+        <v>0.6521061693495026</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6655438127711814</v>
+        <v>0.65700432763917</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6061095171458417</v>
+        <v>0.6369907562528332</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6250109106062356</v>
+        <v>0.6424618973473852</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.626830518162288</v>
+        <v>0.6450118116111375</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6184557479889289</v>
+        <v>0.6414517863830003</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6184557479889289</v>
+        <v>0.6207269138611158</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5985146793408023</v>
+        <v>0.631140559580357</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6172682516844568</v>
+        <v>0.6128202438907644</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6040544516681261</v>
+        <v>0.6130395118805942</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6090965595690945</v>
+        <v>0.6130395118805942</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6090965595690945</v>
+        <v>0.6130395118805942</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5952601510872595</v>
+        <v>0.6114444516399697</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5910532324958681</v>
+        <v>0.6101425699475446</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5396368246334741</v>
+        <v>0.6099018327002835</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5497277275811678</v>
+        <v>0.6121142220808146</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5495704036783525</v>
+        <v>0.5411636055963667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5488481919365693</v>
+        <v>0.5402678800199348</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5098297523081212</v>
+        <v>0.5415845438240338</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5023788641143826</v>
+        <v>0.5427734479486652</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5269101303923032</v>
+        <v>0.5418481581488854</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.556206515954826</v>
+        <v>0.5201184539882138</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5559657787075647</v>
+        <v>0.5153709324556044</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5374462564654141</v>
+        <v>0.5147764803932886</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5369190278157108</v>
+        <v>0.538717166114332</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5434780619384557</v>
+        <v>0.5419072865955812</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4798949203033008</v>
+        <v>0.5405153044129531</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.497276571901599</v>
+        <v>0.5409214605289462</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4972389127123344</v>
+        <v>0.5503492801815525</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4972389127123344</v>
+        <v>0.5418777223722333</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4993436038506697</v>
+        <v>0.5300048710577516</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4995547768745829</v>
+        <v>0.5021666352253498</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4864817588741944</v>
+        <v>0.5006468933632542</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4855054355936355</v>
+        <v>0.5005715749847252</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4749626223747673</v>
+        <v>0.4999771229224094</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4773393747589109</v>
+        <v>0.5000147821116739</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4726442945272399</v>
+        <v>0.4997740448644128</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4595139078553549</v>
+        <v>0.4995709668064163</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4600450080104967</v>
+        <v>0.5001277596794675</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.503519198443514</v>
+        <v>0.5001277596794675</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5039858908263622</v>
+        <v>0.5007222117417832</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.486361038295524</v>
+        <v>0.5004209382276671</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5181186454517555</v>
+        <v>0.5007746530427217</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5348900070109444</v>
+        <v>0.5026857689091364</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5366047319651198</v>
+        <v>0.5021289760360852</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4994435590819886</v>
+        <v>0.5021289760360852</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4977664933170777</v>
+        <v>0.4999771229224094</v>
       </c>
     </row>
   </sheetData>
